--- a/vendor_product/vendor_list.xlsx
+++ b/vendor_product/vendor_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\A Versatile Dataset for Network-Traffic-Based CPS Device Identification\experiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\ICSLibrary\experiment\vendor_product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E8168E-F1DA-48E7-9349-64801A647C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D2B52C-A654-4B35-BC5C-CBF8287DFCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-11304" yWindow="-26028" windowWidth="46296" windowHeight="25536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="124">
   <si>
     <t>ABB</t>
   </si>
@@ -396,14 +396,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>16 corporations</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>25 vendors</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>AMiT spol. s r.o. Praha</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -452,7 +444,51 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>total</t>
+    <t>Siemens</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Siemens is a global technology company specializing in industrial automation, digitalization, and intelligent infrastructure, providing comprehensive solutions across industries such as manufacturing, energy, healthcare, and transportation in over 190 countries, with leading expertise in industrial control systems, smart grid technologies, and intelligent building automation.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCADAs, HMIs, PLCs, sensors, actuators, power equipment, medical equipment.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>18 corporations</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>27 vendors</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIPA</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Yaskawa </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIPA is a German automation company specializing in PLCs, I/O systems, and industrial networking solutions. Founded in 1985 and later acquired by Yaskawa in 2012, VIPA is known for its compatibility with Siemens' SIMATIC systems and innovative high-speed automation solutions.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manufacturing, logistics, and process automation.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Industrial automation, distributed energy resources, rail transport, and health technology.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HMIs, PLCs, SLIO I/O systems, and industrial communication devices.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -460,7 +496,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -493,13 +529,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -597,9 +626,7 @@
       <top style="dotted">
         <color theme="8"/>
       </top>
-      <bottom style="thin">
-        <color theme="8"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -608,57 +635,66 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -964,561 +1000,601 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="19.44140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="38.44140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="34.109375" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="19.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="38.44140625" style="19" customWidth="1"/>
+    <col min="6" max="6" width="34.109375" style="19" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="97.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="95.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="127.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="82.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="222" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="99.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" ht="125.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="55.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="128.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="91.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="59.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="100.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="114.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <v>26</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="C27" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="97.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="95.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="127.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="82.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="222" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="99.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="1:6" ht="125.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="55.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="128.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="91.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="59.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="100.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>23</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="114.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>24</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>25</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="E27" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="94.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
         <v>27</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-    </row>
-    <row r="28" spans="1:6" s="1" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C30" s="4"/>
+      <c r="B28" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C31" s="4"/>
+      <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C32" s="4"/>
+      <c r="C32" s="3"/>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="4"/>
+      <c r="C33" s="3"/>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="4"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="4"/>
+      <c r="C35" s="3"/>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="4"/>
+      <c r="C36" s="3"/>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="4"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C39" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F26">
